--- a/final_data_pipeline/output/325180longform.xlsx
+++ b/final_data_pipeline/output/325180longform.xlsx
@@ -4162,7 +4162,7 @@
         <v>223</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -4254,7 +4254,7 @@
         <v>222</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB35">
         <v>8000</v>
@@ -4343,7 +4343,7 @@
         <v>223</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB36">
         <v>8000</v>
@@ -4435,7 +4435,7 @@
         <v>222</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -5984,7 +5984,7 @@
         <v>223</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -6073,7 +6073,7 @@
         <v>223</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -6165,7 +6165,7 @@
         <v>223</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -6257,7 +6257,7 @@
         <v>222</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -6349,7 +6349,7 @@
         <v>222</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -6441,7 +6441,7 @@
         <v>222</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6533,7 +6533,7 @@
         <v>222</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6625,7 +6625,7 @@
         <v>223</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -7447,7 +7447,7 @@
         <v>223</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -7536,7 +7536,7 @@
         <v>223</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7628,7 +7628,7 @@
         <v>222</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -7720,7 +7720,7 @@
         <v>222</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7812,7 +7812,7 @@
         <v>223</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7904,7 +7904,7 @@
         <v>222</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7993,7 +7993,7 @@
         <v>223</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -8085,7 +8085,7 @@
         <v>222</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -10367,7 +10367,7 @@
         <v>223</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -10456,7 +10456,7 @@
         <v>223</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -10548,7 +10548,7 @@
         <v>222</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -10640,7 +10640,7 @@
         <v>222</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -11462,7 +11462,7 @@
         <v>222</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB114">
         <v>8000</v>
@@ -11551,7 +11551,7 @@
         <v>223</v>
       </c>
       <c r="AA115">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB115">
         <v>8000</v>
@@ -11643,7 +11643,7 @@
         <v>222</v>
       </c>
       <c r="AA116">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB116">
         <v>8000</v>
@@ -11735,7 +11735,7 @@
         <v>223</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -14014,7 +14014,7 @@
         <v>223</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -14103,7 +14103,7 @@
         <v>223</v>
       </c>
       <c r="AA143">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB143">
         <v>8000</v>
@@ -14195,7 +14195,7 @@
         <v>223</v>
       </c>
       <c r="AA144">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB144">
         <v>8000</v>
@@ -14287,7 +14287,7 @@
         <v>222</v>
       </c>
       <c r="AA145">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB145">
         <v>8000</v>
@@ -14379,7 +14379,7 @@
         <v>223</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -14471,7 +14471,7 @@
         <v>222</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -14563,7 +14563,7 @@
         <v>222</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -14655,7 +14655,7 @@
         <v>222</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -14747,7 +14747,7 @@
         <v>222</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -14839,7 +14839,7 @@
         <v>222</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -14928,7 +14928,7 @@
         <v>223</v>
       </c>
       <c r="AA152">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB152">
         <v>8000</v>
@@ -15020,7 +15020,7 @@
         <v>223</v>
       </c>
       <c r="AA153">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB153">
         <v>8000</v>
@@ -15109,7 +15109,7 @@
         <v>223</v>
       </c>
       <c r="AA154">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB154">
         <v>8000</v>
@@ -15201,7 +15201,7 @@
         <v>222</v>
       </c>
       <c r="AA155">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB155">
         <v>8000</v>
@@ -15293,7 +15293,7 @@
         <v>223</v>
       </c>
       <c r="AA156">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB156">
         <v>8000</v>
@@ -15385,7 +15385,7 @@
         <v>222</v>
       </c>
       <c r="AA157">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB157">
         <v>8000</v>
@@ -15842,7 +15842,7 @@
         <v>223</v>
       </c>
       <c r="AA162">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB162">
         <v>8000</v>
@@ -15931,7 +15931,7 @@
         <v>223</v>
       </c>
       <c r="AA163">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB163">
         <v>8000</v>
@@ -16023,7 +16023,7 @@
         <v>222</v>
       </c>
       <c r="AA164">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB164">
         <v>8000</v>
@@ -16115,7 +16115,7 @@
         <v>222</v>
       </c>
       <c r="AA165">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB165">
         <v>8000</v>
@@ -18397,7 +18397,7 @@
         <v>222</v>
       </c>
       <c r="AA190">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB190">
         <v>8000</v>
@@ -18489,7 +18489,7 @@
         <v>222</v>
       </c>
       <c r="AA191">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB191">
         <v>8000</v>
@@ -18581,7 +18581,7 @@
         <v>223</v>
       </c>
       <c r="AA192">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB192">
         <v>8000</v>
@@ -18670,7 +18670,7 @@
         <v>223</v>
       </c>
       <c r="AA193">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB193">
         <v>8000</v>
@@ -19124,7 +19124,7 @@
         <v>223</v>
       </c>
       <c r="AA198">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB198">
         <v>8000</v>
@@ -19216,7 +19216,7 @@
         <v>222</v>
       </c>
       <c r="AA199">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB199">
         <v>8000</v>
@@ -19308,7 +19308,7 @@
         <v>222</v>
       </c>
       <c r="AA200">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB200">
         <v>8000</v>
@@ -19400,7 +19400,7 @@
         <v>223</v>
       </c>
       <c r="AA201">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB201">
         <v>8000</v>
@@ -19495,7 +19495,7 @@
         <v>223</v>
       </c>
       <c r="AA202">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB202">
         <v>8000</v>
@@ -19587,7 +19587,7 @@
         <v>222</v>
       </c>
       <c r="AA203">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB203">
         <v>8000</v>
@@ -19676,7 +19676,7 @@
         <v>223</v>
       </c>
       <c r="AA204">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB204">
         <v>8000</v>
@@ -19768,7 +19768,7 @@
         <v>222</v>
       </c>
       <c r="AA205">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB205">
         <v>8000</v>
@@ -19857,7 +19857,7 @@
         <v>223</v>
       </c>
       <c r="AA206">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB206">
         <v>8000</v>
@@ -19949,7 +19949,7 @@
         <v>222</v>
       </c>
       <c r="AA207">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB207">
         <v>8000</v>
@@ -20041,7 +20041,7 @@
         <v>222</v>
       </c>
       <c r="AA208">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB208">
         <v>8000</v>
@@ -20133,7 +20133,7 @@
         <v>223</v>
       </c>
       <c r="AA209">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB209">
         <v>8000</v>
@@ -20225,7 +20225,7 @@
         <v>223</v>
       </c>
       <c r="AA210">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB210">
         <v>8000</v>
@@ -20317,7 +20317,7 @@
         <v>223</v>
       </c>
       <c r="AA211">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB211">
         <v>8000</v>
@@ -20409,7 +20409,7 @@
         <v>223</v>
       </c>
       <c r="AA212">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB212">
         <v>8000</v>
@@ -20501,7 +20501,7 @@
         <v>223</v>
       </c>
       <c r="AA213">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB213">
         <v>8000</v>
@@ -20593,7 +20593,7 @@
         <v>223</v>
       </c>
       <c r="AA214">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB214">
         <v>8000</v>
@@ -20685,7 +20685,7 @@
         <v>223</v>
       </c>
       <c r="AA215">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB215">
         <v>8000</v>
@@ -20777,7 +20777,7 @@
         <v>223</v>
       </c>
       <c r="AA216">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB216">
         <v>8000</v>
@@ -20869,7 +20869,7 @@
         <v>223</v>
       </c>
       <c r="AA217">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB217">
         <v>8000</v>
@@ -20961,7 +20961,7 @@
         <v>223</v>
       </c>
       <c r="AA218">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB218">
         <v>8000</v>
@@ -21053,7 +21053,7 @@
         <v>222</v>
       </c>
       <c r="AA219">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB219">
         <v>8000</v>
@@ -21145,7 +21145,7 @@
         <v>222</v>
       </c>
       <c r="AA220">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB220">
         <v>8000</v>
@@ -21237,7 +21237,7 @@
         <v>222</v>
       </c>
       <c r="AA221">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB221">
         <v>8000</v>
@@ -21329,7 +21329,7 @@
         <v>222</v>
       </c>
       <c r="AA222">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB222">
         <v>8000</v>
@@ -21421,7 +21421,7 @@
         <v>222</v>
       </c>
       <c r="AA223">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB223">
         <v>8000</v>
@@ -21513,7 +21513,7 @@
         <v>222</v>
       </c>
       <c r="AA224">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB224">
         <v>8000</v>
@@ -21605,7 +21605,7 @@
         <v>222</v>
       </c>
       <c r="AA225">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB225">
         <v>8000</v>
@@ -21697,7 +21697,7 @@
         <v>222</v>
       </c>
       <c r="AA226">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB226">
         <v>8000</v>
@@ -21789,7 +21789,7 @@
         <v>222</v>
       </c>
       <c r="AA227">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB227">
         <v>8000</v>
@@ -21881,7 +21881,7 @@
         <v>222</v>
       </c>
       <c r="AA228">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB228">
         <v>8000</v>
@@ -21973,7 +21973,7 @@
         <v>222</v>
       </c>
       <c r="AA229">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB229">
         <v>8000</v>
@@ -22065,7 +22065,7 @@
         <v>222</v>
       </c>
       <c r="AA230">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB230">
         <v>8000</v>
@@ -22157,7 +22157,7 @@
         <v>223</v>
       </c>
       <c r="AA231">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB231">
         <v>8000</v>
@@ -22249,7 +22249,7 @@
         <v>223</v>
       </c>
       <c r="AA232">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB232">
         <v>8000</v>
@@ -22341,7 +22341,7 @@
         <v>223</v>
       </c>
       <c r="AA233">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB233">
         <v>8000</v>
@@ -22433,7 +22433,7 @@
         <v>222</v>
       </c>
       <c r="AA234">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB234">
         <v>8000</v>
@@ -22522,7 +22522,7 @@
         <v>223</v>
       </c>
       <c r="AA235">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB235">
         <v>8000</v>
@@ -22611,7 +22611,7 @@
         <v>223</v>
       </c>
       <c r="AA236">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB236">
         <v>8000</v>
@@ -22700,7 +22700,7 @@
         <v>223</v>
       </c>
       <c r="AA237">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB237">
         <v>8000</v>
@@ -22789,7 +22789,7 @@
         <v>223</v>
       </c>
       <c r="AA238">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB238">
         <v>8000</v>
@@ -22878,7 +22878,7 @@
         <v>223</v>
       </c>
       <c r="AA239">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB239">
         <v>8000</v>
@@ -22967,7 +22967,7 @@
         <v>223</v>
       </c>
       <c r="AA240">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB240">
         <v>8000</v>
@@ -23059,7 +23059,7 @@
         <v>222</v>
       </c>
       <c r="AA241">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB241">
         <v>8000</v>
@@ -23151,7 +23151,7 @@
         <v>222</v>
       </c>
       <c r="AA242">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB242">
         <v>8000</v>
@@ -23243,7 +23243,7 @@
         <v>222</v>
       </c>
       <c r="AA243">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB243">
         <v>8000</v>
@@ -23332,7 +23332,7 @@
         <v>223</v>
       </c>
       <c r="AA244">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB244">
         <v>8000</v>
@@ -23424,7 +23424,7 @@
         <v>222</v>
       </c>
       <c r="AA245">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB245">
         <v>8000</v>
@@ -23516,7 +23516,7 @@
         <v>222</v>
       </c>
       <c r="AA246">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB246">
         <v>8000</v>
@@ -23608,7 +23608,7 @@
         <v>222</v>
       </c>
       <c r="AA247">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB247">
         <v>8000</v>
@@ -23700,7 +23700,7 @@
         <v>222</v>
       </c>
       <c r="AA248">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB248">
         <v>8000</v>
@@ -23792,7 +23792,7 @@
         <v>222</v>
       </c>
       <c r="AA249">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB249">
         <v>8000</v>
@@ -23884,7 +23884,7 @@
         <v>222</v>
       </c>
       <c r="AA250">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB250">
         <v>8000</v>
@@ -23976,7 +23976,7 @@
         <v>222</v>
       </c>
       <c r="AA251">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB251">
         <v>8000</v>
@@ -24065,7 +24065,7 @@
         <v>223</v>
       </c>
       <c r="AA252">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB252">
         <v>8000</v>
@@ -24154,7 +24154,7 @@
         <v>223</v>
       </c>
       <c r="AA253">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB253">
         <v>8000</v>
@@ -24243,7 +24243,7 @@
         <v>223</v>
       </c>
       <c r="AA254">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB254">
         <v>8000</v>
@@ -24332,7 +24332,7 @@
         <v>223</v>
       </c>
       <c r="AA255">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB255">
         <v>8000</v>
@@ -24424,7 +24424,7 @@
         <v>222</v>
       </c>
       <c r="AA256">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB256">
         <v>8000</v>
@@ -24513,7 +24513,7 @@
         <v>223</v>
       </c>
       <c r="AA257">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB257">
         <v>8000</v>
@@ -24967,7 +24967,7 @@
         <v>223</v>
       </c>
       <c r="AA262">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB262">
         <v>8000</v>
@@ -25059,7 +25059,7 @@
         <v>223</v>
       </c>
       <c r="AA263">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB263">
         <v>8000</v>
@@ -25151,7 +25151,7 @@
         <v>222</v>
       </c>
       <c r="AA264">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB264">
         <v>8000</v>
@@ -25243,7 +25243,7 @@
         <v>222</v>
       </c>
       <c r="AA265">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB265">
         <v>8000</v>
@@ -25335,7 +25335,7 @@
         <v>223</v>
       </c>
       <c r="AA266">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB266">
         <v>8000</v>
@@ -25424,7 +25424,7 @@
         <v>223</v>
       </c>
       <c r="AA267">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB267">
         <v>8000</v>
@@ -25516,7 +25516,7 @@
         <v>222</v>
       </c>
       <c r="AA268">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB268">
         <v>8000</v>
@@ -25608,7 +25608,7 @@
         <v>222</v>
       </c>
       <c r="AA269">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB269">
         <v>8000</v>
@@ -30445,7 +30445,7 @@
         <v>223</v>
       </c>
       <c r="AA322">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB322">
         <v>8000</v>
@@ -30537,7 +30537,7 @@
         <v>222</v>
       </c>
       <c r="AA323">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB323">
         <v>8000</v>
@@ -30629,7 +30629,7 @@
         <v>222</v>
       </c>
       <c r="AA324">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB324">
         <v>8000</v>
@@ -30718,7 +30718,7 @@
         <v>223</v>
       </c>
       <c r="AA325">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB325">
         <v>8000</v>
@@ -30810,7 +30810,7 @@
         <v>223</v>
       </c>
       <c r="AA326">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB326">
         <v>8000</v>
@@ -30899,7 +30899,7 @@
         <v>223</v>
       </c>
       <c r="AA327">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB327">
         <v>8000</v>
@@ -30991,7 +30991,7 @@
         <v>222</v>
       </c>
       <c r="AA328">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB328">
         <v>8000</v>
@@ -31083,7 +31083,7 @@
         <v>222</v>
       </c>
       <c r="AA329">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB329">
         <v>8000</v>
@@ -31175,7 +31175,7 @@
         <v>222</v>
       </c>
       <c r="AA330">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB330">
         <v>8000</v>
@@ -31267,7 +31267,7 @@
         <v>223</v>
       </c>
       <c r="AA331">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB331">
         <v>8000</v>
@@ -31359,7 +31359,7 @@
         <v>223</v>
       </c>
       <c r="AA332">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB332">
         <v>8000</v>
@@ -31448,7 +31448,7 @@
         <v>223</v>
       </c>
       <c r="AA333">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB333">
         <v>8000</v>
@@ -31537,7 +31537,7 @@
         <v>223</v>
       </c>
       <c r="AA334">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB334">
         <v>8000</v>
@@ -31626,7 +31626,7 @@
         <v>223</v>
       </c>
       <c r="AA335">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB335">
         <v>8000</v>
@@ -31718,7 +31718,7 @@
         <v>222</v>
       </c>
       <c r="AA336">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB336">
         <v>8000</v>
@@ -31810,7 +31810,7 @@
         <v>222</v>
       </c>
       <c r="AA337">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB337">
         <v>8000</v>
@@ -31902,7 +31902,7 @@
         <v>223</v>
       </c>
       <c r="AA338">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB338">
         <v>8000</v>
@@ -31994,7 +31994,7 @@
         <v>222</v>
       </c>
       <c r="AA339">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB339">
         <v>8000</v>
@@ -32086,7 +32086,7 @@
         <v>222</v>
       </c>
       <c r="AA340">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB340">
         <v>8000</v>
@@ -32175,7 +32175,7 @@
         <v>223</v>
       </c>
       <c r="AA341">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB341">
         <v>8000</v>
@@ -32267,7 +32267,7 @@
         <v>223</v>
       </c>
       <c r="AA342">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB342">
         <v>8000</v>
@@ -32356,7 +32356,7 @@
         <v>223</v>
       </c>
       <c r="AA343">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB343">
         <v>8000</v>
@@ -32448,7 +32448,7 @@
         <v>222</v>
       </c>
       <c r="AA344">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB344">
         <v>8000</v>
@@ -32540,7 +32540,7 @@
         <v>222</v>
       </c>
       <c r="AA345">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB345">
         <v>8000</v>
@@ -32632,7 +32632,7 @@
         <v>222</v>
       </c>
       <c r="AA346">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB346">
         <v>8000</v>
@@ -32724,7 +32724,7 @@
         <v>222</v>
       </c>
       <c r="AA347">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB347">
         <v>8000</v>
@@ -32816,7 +32816,7 @@
         <v>222</v>
       </c>
       <c r="AA348">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB348">
         <v>8000</v>
@@ -32908,7 +32908,7 @@
         <v>223</v>
       </c>
       <c r="AA349">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB349">
         <v>8000</v>
@@ -35190,7 +35190,7 @@
         <v>223</v>
       </c>
       <c r="AA374">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB374">
         <v>8000</v>
@@ -35282,7 +35282,7 @@
         <v>222</v>
       </c>
       <c r="AA375">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB375">
         <v>8000</v>
@@ -35374,7 +35374,7 @@
         <v>222</v>
       </c>
       <c r="AA376">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB376">
         <v>8000</v>
@@ -35463,7 +35463,7 @@
         <v>223</v>
       </c>
       <c r="AA377">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB377">
         <v>8000</v>
@@ -35555,7 +35555,7 @@
         <v>222</v>
       </c>
       <c r="AA378">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB378">
         <v>8000</v>
@@ -35647,7 +35647,7 @@
         <v>222</v>
       </c>
       <c r="AA379">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB379">
         <v>8000</v>
@@ -35739,7 +35739,7 @@
         <v>223</v>
       </c>
       <c r="AA380">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB380">
         <v>8000</v>
@@ -35828,7 +35828,7 @@
         <v>223</v>
       </c>
       <c r="AA381">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB381">
         <v>8000</v>
@@ -35917,7 +35917,7 @@
         <v>223</v>
       </c>
       <c r="AA382">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB382">
         <v>8000</v>
@@ -36009,7 +36009,7 @@
         <v>222</v>
       </c>
       <c r="AA383">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB383">
         <v>8000</v>
@@ -36101,7 +36101,7 @@
         <v>223</v>
       </c>
       <c r="AA384">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB384">
         <v>8000</v>
@@ -36193,7 +36193,7 @@
         <v>222</v>
       </c>
       <c r="AA385">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB385">
         <v>8000</v>
@@ -37742,7 +37742,7 @@
         <v>223</v>
       </c>
       <c r="AA402">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB402">
         <v>8000</v>
@@ -37834,7 +37834,7 @@
         <v>222</v>
       </c>
       <c r="AA403">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB403">
         <v>8000</v>
@@ -37926,7 +37926,7 @@
         <v>222</v>
       </c>
       <c r="AA404">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB404">
         <v>8000</v>
@@ -38018,7 +38018,7 @@
         <v>223</v>
       </c>
       <c r="AA405">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB405">
         <v>8000</v>
@@ -38107,7 +38107,7 @@
         <v>223</v>
       </c>
       <c r="AA406">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB406">
         <v>8000</v>
@@ -38199,7 +38199,7 @@
         <v>223</v>
       </c>
       <c r="AA407">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB407">
         <v>8000</v>
@@ -38291,7 +38291,7 @@
         <v>222</v>
       </c>
       <c r="AA408">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB408">
         <v>8000</v>
@@ -38383,7 +38383,7 @@
         <v>222</v>
       </c>
       <c r="AA409">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB409">
         <v>8000</v>
@@ -38475,7 +38475,7 @@
         <v>222</v>
       </c>
       <c r="AA410">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB410">
         <v>8000</v>
@@ -38567,7 +38567,7 @@
         <v>222</v>
       </c>
       <c r="AA411">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB411">
         <v>8000</v>
@@ -38659,7 +38659,7 @@
         <v>222</v>
       </c>
       <c r="AA412">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB412">
         <v>8000</v>
@@ -38751,7 +38751,7 @@
         <v>222</v>
       </c>
       <c r="AA413">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB413">
         <v>8000</v>
@@ -38843,7 +38843,7 @@
         <v>222</v>
       </c>
       <c r="AA414">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB414">
         <v>8000</v>
@@ -38935,7 +38935,7 @@
         <v>223</v>
       </c>
       <c r="AA415">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB415">
         <v>8000</v>
@@ -39027,7 +39027,7 @@
         <v>223</v>
       </c>
       <c r="AA416">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB416">
         <v>8000</v>
@@ -39119,7 +39119,7 @@
         <v>223</v>
       </c>
       <c r="AA417">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB417">
         <v>8000</v>
@@ -39208,7 +39208,7 @@
         <v>223</v>
       </c>
       <c r="AA418">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB418">
         <v>8000</v>
@@ -39297,7 +39297,7 @@
         <v>223</v>
       </c>
       <c r="AA419">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB419">
         <v>8000</v>
@@ -39386,7 +39386,7 @@
         <v>223</v>
       </c>
       <c r="AA420">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB420">
         <v>8000</v>
@@ -39475,7 +39475,7 @@
         <v>223</v>
       </c>
       <c r="AA421">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB421">
         <v>8000</v>
@@ -39564,7 +39564,7 @@
         <v>223</v>
       </c>
       <c r="AA422">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB422">
         <v>8000</v>
@@ -39656,7 +39656,7 @@
         <v>223</v>
       </c>
       <c r="AA423">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB423">
         <v>8000</v>
@@ -39748,7 +39748,7 @@
         <v>223</v>
       </c>
       <c r="AA424">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB424">
         <v>8000</v>
@@ -39840,7 +39840,7 @@
         <v>222</v>
       </c>
       <c r="AA425">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB425">
         <v>8000</v>
@@ -39932,7 +39932,7 @@
         <v>222</v>
       </c>
       <c r="AA426">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB426">
         <v>8000</v>
@@ -40024,7 +40024,7 @@
         <v>222</v>
       </c>
       <c r="AA427">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB427">
         <v>8000</v>
@@ -40116,7 +40116,7 @@
         <v>222</v>
       </c>
       <c r="AA428">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB428">
         <v>8000</v>
@@ -40208,7 +40208,7 @@
         <v>222</v>
       </c>
       <c r="AA429">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB429">
         <v>8000</v>
@@ -40300,7 +40300,7 @@
         <v>222</v>
       </c>
       <c r="AA430">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB430">
         <v>8000</v>
@@ -40389,7 +40389,7 @@
         <v>223</v>
       </c>
       <c r="AA431">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB431">
         <v>8000</v>
@@ -40481,7 +40481,7 @@
         <v>222</v>
       </c>
       <c r="AA432">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB432">
         <v>8000</v>
@@ -40573,7 +40573,7 @@
         <v>223</v>
       </c>
       <c r="AA433">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AB433">
         <v>8000</v>
